--- a/_Rarzrabotki/notebook/specs/2026-10-02-ekonomiya-materialiv-ss-irc-ANALIZ.xlsx
+++ b/_Rarzrabotki/notebook/specs/2026-10-02-ekonomiya-materialiv-ss-irc-ANALIZ.xlsx
@@ -8069,7 +8069,7 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>сопоставимо</t>
+          <t>единица/состав</t>
         </is>
       </c>
       <c r="AI49" t="n">
@@ -16313,7 +16313,7 @@
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>сопоставимо</t>
+          <t>единица/состав</t>
         </is>
       </c>
       <c r="AI101" t="n">
@@ -21571,7 +21571,7 @@
       </c>
       <c r="AH134" t="inlineStr">
         <is>
-          <t>сопоставимо</t>
+          <t>единица/состав</t>
         </is>
       </c>
       <c r="AI134" t="n">
